--- a/Hoàng/2025/T5/CHI NHÁNH CÔNG TY TNHH AUTOGRILL VFS F&B TẠI ĐÀ NẴNG (78-2025)/DS, DM CHI NHÁNH CÔNG TY TNHH AUTOGRILL VFS F&B TẠI ĐÀ NẴNG.xlsx
+++ b/Hoàng/2025/T5/CHI NHÁNH CÔNG TY TNHH AUTOGRILL VFS F&B TẠI ĐÀ NẴNG (78-2025)/DS, DM CHI NHÁNH CÔNG TY TNHH AUTOGRILL VFS F&B TẠI ĐÀ NẴNG.xlsx
@@ -5,21 +5,22 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\DATA-TN\Hoàng\2025\CHI NHÁNH CÔNG TY TNHH AUTOGRILL VFS F&amp;B TẠI ĐÀ NẴNG (78-2025)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\DATA-TN\Hoàng\2025\T5\CHI NHÁNH CÔNG TY TNHH AUTOGRILL VFS F&amp;B TẠI ĐÀ NẴNG (78-2025)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65F47662-2413-4847-AD4D-F2371555165F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9EA52CA-149C-4BAB-85E7-691D1B488561}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DS (2)" sheetId="3" state="hidden" r:id="rId1"/>
-    <sheet name="DS" sheetId="1" r:id="rId2"/>
-    <sheet name="DM" sheetId="4" r:id="rId3"/>
+    <sheet name="DS_ORI" sheetId="1" state="hidden" r:id="rId2"/>
+    <sheet name="DS" sheetId="5" r:id="rId3"/>
+    <sheet name="DM" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">DS!$A$1:$G$24</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">DM!$A$1:$C$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">DS_ORI!$A$1:$G$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">DM!$A$1:$C$34</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="116">
   <si>
     <t>STT</t>
   </si>
@@ -430,7 +431,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -521,6 +522,13 @@
     </font>
     <font>
       <sz val="13"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -650,7 +658,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -719,9 +727,6 @@
     <xf numFmtId="3" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="7" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -733,6 +738,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2376,6 +2396,431 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89B64BB5-20AB-4FC0-A85B-663EFCFF3006}">
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" s="33" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" s="33" t="s">
+        <v>78</v>
+      </c>
+      <c r="E1" s="33" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="34">
+        <v>1</v>
+      </c>
+      <c r="B2" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="36" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2" s="34">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="34">
+        <v>2</v>
+      </c>
+      <c r="B3" s="34" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="35" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="36" t="s">
+        <v>79</v>
+      </c>
+      <c r="E3" s="34">
+        <v>1986</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="34">
+        <v>3</v>
+      </c>
+      <c r="B4" s="34" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="36" t="s">
+        <v>79</v>
+      </c>
+      <c r="E4" s="34">
+        <v>1968</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="34">
+        <v>4</v>
+      </c>
+      <c r="B5" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="36" t="s">
+        <v>79</v>
+      </c>
+      <c r="E5" s="34">
+        <v>1988</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="34">
+        <v>5</v>
+      </c>
+      <c r="B6" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="36" t="s">
+        <v>79</v>
+      </c>
+      <c r="E6" s="34">
+        <v>1976</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="34">
+        <v>6</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="36" t="s">
+        <v>79</v>
+      </c>
+      <c r="E7" s="34">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="34">
+        <v>7</v>
+      </c>
+      <c r="B8" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="36" t="s">
+        <v>79</v>
+      </c>
+      <c r="E8" s="34">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="34">
+        <v>8</v>
+      </c>
+      <c r="B9" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="36" t="s">
+        <v>79</v>
+      </c>
+      <c r="E9" s="34">
+        <v>1985</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="34">
+        <v>9</v>
+      </c>
+      <c r="B10" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="D10" s="36" t="s">
+        <v>79</v>
+      </c>
+      <c r="E10" s="34">
+        <v>1991</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="34">
+        <v>10</v>
+      </c>
+      <c r="B11" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" s="36" t="s">
+        <v>79</v>
+      </c>
+      <c r="E11" s="34">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="34">
+        <v>11</v>
+      </c>
+      <c r="B12" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="D12" s="36" t="s">
+        <v>79</v>
+      </c>
+      <c r="E12" s="34">
+        <v>1985</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="34">
+        <v>12</v>
+      </c>
+      <c r="B13" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" s="36" t="s">
+        <v>80</v>
+      </c>
+      <c r="E13" s="34">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="34">
+        <v>13</v>
+      </c>
+      <c r="B14" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="36" t="s">
+        <v>80</v>
+      </c>
+      <c r="E14" s="34">
+        <v>1981</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="34">
+        <v>14</v>
+      </c>
+      <c r="B15" s="34" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="36" t="s">
+        <v>80</v>
+      </c>
+      <c r="E15" s="34">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="34">
+        <v>15</v>
+      </c>
+      <c r="B16" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="36" t="s">
+        <v>80</v>
+      </c>
+      <c r="E16" s="34">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="34">
+        <v>16</v>
+      </c>
+      <c r="B17" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="36" t="s">
+        <v>80</v>
+      </c>
+      <c r="E17" s="34">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="34">
+        <v>17</v>
+      </c>
+      <c r="B18" s="34" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18" s="36" t="s">
+        <v>80</v>
+      </c>
+      <c r="E18" s="34">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="34">
+        <v>18</v>
+      </c>
+      <c r="B19" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19" s="36" t="s">
+        <v>80</v>
+      </c>
+      <c r="E19" s="34">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="34">
+        <v>19</v>
+      </c>
+      <c r="B20" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" s="36" t="s">
+        <v>80</v>
+      </c>
+      <c r="E20" s="34">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="34">
+        <v>20</v>
+      </c>
+      <c r="B21" s="34" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="35" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" s="36" t="s">
+        <v>80</v>
+      </c>
+      <c r="E21" s="34">
+        <v>1997</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="34">
+        <v>21</v>
+      </c>
+      <c r="B22" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" s="36" t="s">
+        <v>80</v>
+      </c>
+      <c r="E22" s="34">
+        <v>1994</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="34">
+        <v>22</v>
+      </c>
+      <c r="B23" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" s="35" t="s">
+        <v>61</v>
+      </c>
+      <c r="D23" s="36" t="s">
+        <v>80</v>
+      </c>
+      <c r="E23" s="34">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="34">
+        <v>23</v>
+      </c>
+      <c r="B24" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="C24" s="35" t="s">
+        <v>67</v>
+      </c>
+      <c r="D24" s="36" t="s">
+        <v>80</v>
+      </c>
+      <c r="E24" s="34">
+        <v>1988</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B63BAFE4-029A-4E49-93A3-83BD5C7A9884}">
   <dimension ref="A1:D47"/>
   <sheetFormatPr defaultColWidth="8" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2386,14 +2831,14 @@
     <col min="4" max="16384" width="8" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="C1" s="29" t="s">
         <v>115</v>
       </c>
     </row>
@@ -2421,11 +2866,11 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="37" t="s">
         <v>84</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="31"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="30"/>
     </row>
     <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
@@ -2536,7 +2981,7 @@
       <c r="C14" s="15">
         <v>12</v>
       </c>
-      <c r="D14" s="29"/>
+      <c r="D14" s="28"/>
     </row>
     <row r="15" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
@@ -2548,7 +2993,7 @@
       <c r="C15" s="15">
         <v>12</v>
       </c>
-      <c r="D15" s="29"/>
+      <c r="D15" s="28"/>
     </row>
     <row r="16" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
@@ -2642,7 +3087,7 @@
       <c r="A24" s="9">
         <v>22</v>
       </c>
-      <c r="B24" s="33" t="s">
+      <c r="B24" s="32" t="s">
         <v>104</v>
       </c>
       <c r="C24" s="11">
@@ -2650,11 +3095,11 @@
       </c>
     </row>
     <row r="25" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="28" t="s">
+      <c r="A25" s="37" t="s">
         <v>105</v>
       </c>
-      <c r="B25" s="28"/>
-      <c r="C25" s="31"/>
+      <c r="B25" s="37"/>
+      <c r="C25" s="30"/>
     </row>
     <row r="26" spans="1:3" s="22" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="13">
@@ -2663,7 +3108,7 @@
       <c r="B26" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="C26" s="32">
+      <c r="C26" s="31">
         <v>23</v>
       </c>
     </row>
